--- a/ميديكسا.xlsx
+++ b/ميديكسا.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C66B5C8-DE18-4577-A983-18DA1B6DA8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0F28C2-B06E-418C-A79E-02ADB668746D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="96">
   <si>
     <t>الرقم</t>
   </si>
@@ -319,6 +319,9 @@
   <si>
     <t>مريم الفلاحات</t>
   </si>
+  <si>
+    <t>بسمه عبدالله خليل السعيدات</t>
+  </si>
 </sst>
 </file>
 
@@ -379,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -388,14 +391,14 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
@@ -463,118 +466,6 @@
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
     <dxf>
@@ -635,6 +526,31 @@
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <strike val="0"/>
@@ -654,11 +570,13 @@
     <dxf>
       <font>
         <b/>
+        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color indexed="8"/>
@@ -686,6 +604,24 @@
     <dxf>
       <font>
         <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
@@ -702,11 +638,81 @@
     <dxf>
       <font>
         <b/>
+        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color indexed="8"/>
@@ -767,25 +773,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M258" totalsRowCount="1" headerRowDxfId="26">
-  <autoFilter ref="A1:M257" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M284" totalsRowCount="1" headerRowDxfId="26">
+  <autoFilter ref="A1:M283" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M257">
     <sortCondition ref="F1:F257"/>
   </sortState>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="الرقم" dataDxfId="25" totalsRowDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="رقم الموظف /رقم البطاقة" dataDxfId="24" totalsRowDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="اسم المريض" dataDxfId="23" totalsRowDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="رقم النموذج" dataDxfId="22" totalsRowDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="نوع المستفيد" dataDxfId="21" totalsRowDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="تاريخ البيع" dataDxfId="20" totalsRowDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="قيمة الفاتورة" dataDxfId="19" totalsRowDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="قيمة المشاركة" dataDxfId="18" totalsRowDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="صافي القيمة" dataDxfId="17" totalsRowDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="القيمة المطلوبة" dataDxfId="16" totalsRowDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="المدفوع" totalsRowFunction="sum" dataDxfId="15" totalsRowDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="المتبقي" dataDxfId="14" totalsRowDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{041AFAF5-9550-455C-B55D-99C85FD7E974}" name="تاريخ الدفعة" dataDxfId="13" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="الرقم" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="رقم الموظف /رقم البطاقة" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="اسم المريض" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="رقم النموذج" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="نوع المستفيد" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="تاريخ البيع" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="قيمة الفاتورة" dataDxfId="11" totalsRowDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="قيمة المشاركة" dataDxfId="10" totalsRowDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="صافي القيمة" dataDxfId="9" totalsRowDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="القيمة المطلوبة" dataDxfId="8" totalsRowDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="المدفوع" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="المتبقي" dataDxfId="6" totalsRowDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{041AFAF5-9550-455C-B55D-99C85FD7E974}" name="تاريخ الدفعة" dataDxfId="13" totalsRowDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1108,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M258"/>
+  <dimension ref="A1:M284"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.19921875" customWidth="1"/>
@@ -9287,14 +9293,14 @@
         <v>35.872</v>
       </c>
       <c r="J194" s="7">
-        <f t="shared" ref="J194:J257" si="6">G194*0.94-H194</f>
+        <f t="shared" ref="J194:J258" si="6">G194*0.94-H194</f>
         <v>33.181600000000003</v>
       </c>
       <c r="K194" s="7">
         <v>33.182000000000002</v>
       </c>
       <c r="L194" s="7">
-        <f t="shared" ref="L194:L257" si="7">J194-K194</f>
+        <f t="shared" ref="L194:L258" si="7">J194-K194</f>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M194" s="4">
@@ -11836,20 +11842,1020 @@
       <c r="M257" s="4"/>
     </row>
     <row r="258" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A258" s="2"/>
-      <c r="B258" s="2"/>
-      <c r="C258" s="2"/>
-      <c r="D258" s="2"/>
-      <c r="E258" s="2"/>
-      <c r="F258" s="3"/>
-      <c r="G258" s="6"/>
-      <c r="H258" s="6"/>
-      <c r="I258" s="6"/>
-      <c r="K258" s="7">
+      <c r="A258" s="9">
+        <v>1</v>
+      </c>
+      <c r="B258" s="9">
+        <v>118021</v>
+      </c>
+      <c r="C258" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D258" s="9">
+        <v>178721</v>
+      </c>
+      <c r="E258" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F258" s="10">
+        <v>46204</v>
+      </c>
+      <c r="G258" s="9">
+        <v>56.75</v>
+      </c>
+      <c r="H258" s="9">
+        <v>11.35</v>
+      </c>
+      <c r="I258" s="9">
+        <v>45.4</v>
+      </c>
+      <c r="J258" s="7">
+        <f t="shared" si="6"/>
+        <v>41.994999999999997</v>
+      </c>
+      <c r="K258" s="8"/>
+      <c r="L258" s="7">
+        <f t="shared" si="7"/>
+        <v>41.994999999999997</v>
+      </c>
+      <c r="M258" s="4"/>
+    </row>
+    <row r="259" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A259" s="9">
+        <v>2</v>
+      </c>
+      <c r="B259" s="9">
+        <v>114658</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D259" s="9">
+        <v>2316324</v>
+      </c>
+      <c r="E259" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F259" s="10">
+        <v>46204</v>
+      </c>
+      <c r="G259" s="9">
+        <v>28.75</v>
+      </c>
+      <c r="H259" s="9">
+        <v>5.75</v>
+      </c>
+      <c r="I259" s="9">
+        <v>23</v>
+      </c>
+      <c r="J259" s="7">
+        <f t="shared" ref="J259:J283" si="8">G259*0.94-H259</f>
+        <v>21.274999999999999</v>
+      </c>
+      <c r="K259" s="8"/>
+      <c r="L259" s="7">
+        <f t="shared" ref="L259:L283" si="9">J259-K259</f>
+        <v>21.274999999999999</v>
+      </c>
+      <c r="M259" s="4"/>
+    </row>
+    <row r="260" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A260" s="9">
+        <v>3</v>
+      </c>
+      <c r="B260" s="9">
+        <v>114156</v>
+      </c>
+      <c r="C260" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D260" s="9">
+        <v>2318050</v>
+      </c>
+      <c r="E260" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F260" s="10">
+        <v>46205</v>
+      </c>
+      <c r="G260" s="9">
+        <v>97.53</v>
+      </c>
+      <c r="H260" s="9">
+        <v>19.506</v>
+      </c>
+      <c r="I260" s="9">
+        <v>78.024000000000001</v>
+      </c>
+      <c r="J260" s="7">
+        <f t="shared" si="8"/>
+        <v>72.172199999999989</v>
+      </c>
+      <c r="K260" s="8"/>
+      <c r="L260" s="7">
+        <f t="shared" si="9"/>
+        <v>72.172199999999989</v>
+      </c>
+      <c r="M260" s="4"/>
+    </row>
+    <row r="261" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A261" s="9">
+        <v>4</v>
+      </c>
+      <c r="B261" s="9">
+        <v>139514</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D261" s="9">
+        <v>179072</v>
+      </c>
+      <c r="E261" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F261" s="10">
+        <v>46205</v>
+      </c>
+      <c r="G261" s="9">
+        <v>11.63</v>
+      </c>
+      <c r="H261" s="9">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="I261" s="9">
+        <v>9.3040000000000003</v>
+      </c>
+      <c r="J261" s="7">
+        <f t="shared" si="8"/>
+        <v>8.6061999999999994</v>
+      </c>
+      <c r="K261" s="8"/>
+      <c r="L261" s="7">
+        <f t="shared" si="9"/>
+        <v>8.6061999999999994</v>
+      </c>
+      <c r="M261" s="4"/>
+    </row>
+    <row r="262" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A262" s="9">
+        <v>5</v>
+      </c>
+      <c r="B262" s="9">
+        <v>131204</v>
+      </c>
+      <c r="C262" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D262" s="9">
+        <v>2319012</v>
+      </c>
+      <c r="E262" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F262" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G262" s="9">
+        <v>118.14</v>
+      </c>
+      <c r="H262" s="9">
+        <v>23.628</v>
+      </c>
+      <c r="I262" s="9">
+        <v>94.512</v>
+      </c>
+      <c r="J262" s="7">
+        <f t="shared" si="8"/>
+        <v>87.423599999999993</v>
+      </c>
+      <c r="K262" s="8"/>
+      <c r="L262" s="7">
+        <f t="shared" si="9"/>
+        <v>87.423599999999993</v>
+      </c>
+      <c r="M262" s="4"/>
+    </row>
+    <row r="263" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A263" s="9">
+        <v>6</v>
+      </c>
+      <c r="B263" s="9">
+        <v>131232</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D263" s="9">
+        <v>2319042</v>
+      </c>
+      <c r="E263" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F263" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G263" s="9">
+        <v>44.84</v>
+      </c>
+      <c r="H263" s="9">
+        <v>8.968</v>
+      </c>
+      <c r="I263" s="9">
+        <v>35.872</v>
+      </c>
+      <c r="J263" s="7">
+        <f t="shared" si="8"/>
+        <v>33.181600000000003</v>
+      </c>
+      <c r="K263" s="8"/>
+      <c r="L263" s="7">
+        <f t="shared" si="9"/>
+        <v>33.181600000000003</v>
+      </c>
+      <c r="M263" s="4"/>
+    </row>
+    <row r="264" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A264" s="9">
+        <v>7</v>
+      </c>
+      <c r="B264" s="9">
+        <v>132009</v>
+      </c>
+      <c r="C264" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D264" s="9">
+        <v>2319048</v>
+      </c>
+      <c r="E264" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F264" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G264" s="9">
+        <v>25.74</v>
+      </c>
+      <c r="H264" s="9">
+        <v>5.1479999999999997</v>
+      </c>
+      <c r="I264" s="9">
+        <v>20.591999999999999</v>
+      </c>
+      <c r="J264" s="7">
+        <f t="shared" si="8"/>
+        <v>19.047599999999999</v>
+      </c>
+      <c r="K264" s="8"/>
+      <c r="L264" s="7">
+        <f t="shared" si="9"/>
+        <v>19.047599999999999</v>
+      </c>
+      <c r="M264" s="4"/>
+    </row>
+    <row r="265" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A265" s="9">
+        <v>8</v>
+      </c>
+      <c r="B265" s="9">
+        <v>132070</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D265" s="9">
+        <v>2319049</v>
+      </c>
+      <c r="E265" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F265" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G265" s="9">
+        <v>183.26</v>
+      </c>
+      <c r="H265" s="9">
+        <v>36.652000000000001</v>
+      </c>
+      <c r="I265" s="9">
+        <v>146.608</v>
+      </c>
+      <c r="J265" s="7">
+        <f t="shared" si="8"/>
+        <v>135.61239999999998</v>
+      </c>
+      <c r="K265" s="8"/>
+      <c r="L265" s="7">
+        <f t="shared" si="9"/>
+        <v>135.61239999999998</v>
+      </c>
+      <c r="M265" s="4"/>
+    </row>
+    <row r="266" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A266" s="9">
+        <v>9</v>
+      </c>
+      <c r="B266" s="9">
+        <v>132129</v>
+      </c>
+      <c r="C266" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D266" s="9">
+        <v>2319051</v>
+      </c>
+      <c r="E266" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F266" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G266" s="9">
+        <v>59.98</v>
+      </c>
+      <c r="H266" s="9">
+        <v>11.996</v>
+      </c>
+      <c r="I266" s="9">
+        <v>47.984000000000002</v>
+      </c>
+      <c r="J266" s="7">
+        <f t="shared" si="8"/>
+        <v>44.38519999999999</v>
+      </c>
+      <c r="K266" s="8"/>
+      <c r="L266" s="7">
+        <f t="shared" si="9"/>
+        <v>44.38519999999999</v>
+      </c>
+      <c r="M266" s="4"/>
+    </row>
+    <row r="267" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A267" s="9">
+        <v>10</v>
+      </c>
+      <c r="B267" s="9">
+        <v>134600</v>
+      </c>
+      <c r="C267" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D267" s="9">
+        <v>2319068</v>
+      </c>
+      <c r="E267" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F267" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G267" s="9">
+        <v>118.89</v>
+      </c>
+      <c r="H267" s="9">
+        <v>23.777999999999999</v>
+      </c>
+      <c r="I267" s="9">
+        <v>95.111999999999995</v>
+      </c>
+      <c r="J267" s="7">
+        <f t="shared" si="8"/>
+        <v>87.9786</v>
+      </c>
+      <c r="K267" s="8"/>
+      <c r="L267" s="7">
+        <f t="shared" si="9"/>
+        <v>87.9786</v>
+      </c>
+      <c r="M267" s="4"/>
+    </row>
+    <row r="268" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A268" s="9">
+        <v>11</v>
+      </c>
+      <c r="B268" s="9">
+        <v>134714</v>
+      </c>
+      <c r="C268" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D268" s="9">
+        <v>2319077</v>
+      </c>
+      <c r="E268" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F268" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G268" s="9">
+        <v>242.48</v>
+      </c>
+      <c r="H268" s="9">
+        <v>48.496000000000002</v>
+      </c>
+      <c r="I268" s="9">
+        <v>193.98400000000001</v>
+      </c>
+      <c r="J268" s="7">
+        <f t="shared" si="8"/>
+        <v>179.43519999999998</v>
+      </c>
+      <c r="K268" s="8"/>
+      <c r="L268" s="7">
+        <f t="shared" si="9"/>
+        <v>179.43519999999998</v>
+      </c>
+      <c r="M268" s="4"/>
+    </row>
+    <row r="269" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A269" s="9">
+        <v>12</v>
+      </c>
+      <c r="B269" s="9">
+        <v>137683</v>
+      </c>
+      <c r="C269" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D269" s="9">
+        <v>2319085</v>
+      </c>
+      <c r="E269" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F269" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G269" s="9">
+        <v>130.43</v>
+      </c>
+      <c r="H269" s="9">
+        <v>26.085999999999999</v>
+      </c>
+      <c r="I269" s="9">
+        <v>104.34399999999999</v>
+      </c>
+      <c r="J269" s="7">
+        <f t="shared" si="8"/>
+        <v>96.518200000000007</v>
+      </c>
+      <c r="K269" s="8"/>
+      <c r="L269" s="7">
+        <f t="shared" si="9"/>
+        <v>96.518200000000007</v>
+      </c>
+      <c r="M269" s="4"/>
+    </row>
+    <row r="270" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A270" s="9">
+        <v>13</v>
+      </c>
+      <c r="B270" s="9">
+        <v>138275</v>
+      </c>
+      <c r="C270" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D270" s="9">
+        <v>2319144</v>
+      </c>
+      <c r="E270" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F270" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G270" s="9">
+        <v>52.83</v>
+      </c>
+      <c r="H270" s="9">
+        <v>10.566000000000001</v>
+      </c>
+      <c r="I270" s="9">
+        <v>42.264000000000003</v>
+      </c>
+      <c r="J270" s="7">
+        <f t="shared" si="8"/>
+        <v>39.094199999999994</v>
+      </c>
+      <c r="L270" s="7">
+        <f t="shared" si="9"/>
+        <v>39.094199999999994</v>
+      </c>
+      <c r="M270" s="4"/>
+    </row>
+    <row r="271" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A271" s="9">
+        <v>14</v>
+      </c>
+      <c r="B271" s="9">
+        <v>139514</v>
+      </c>
+      <c r="C271" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D271" s="9">
+        <v>2319145</v>
+      </c>
+      <c r="E271" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F271" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G271" s="9">
+        <v>12.1</v>
+      </c>
+      <c r="H271" s="9">
+        <v>2.42</v>
+      </c>
+      <c r="I271" s="9">
+        <v>9.68</v>
+      </c>
+      <c r="J271" s="7">
+        <f t="shared" si="8"/>
+        <v>8.9539999999999988</v>
+      </c>
+      <c r="L271" s="7">
+        <f t="shared" si="9"/>
+        <v>8.9539999999999988</v>
+      </c>
+      <c r="M271" s="4"/>
+    </row>
+    <row r="272" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A272" s="9">
+        <v>15</v>
+      </c>
+      <c r="B272" s="9">
+        <v>139979</v>
+      </c>
+      <c r="C272" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D272" s="9">
+        <v>2319146</v>
+      </c>
+      <c r="E272" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F272" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G272" s="9">
+        <v>89.16</v>
+      </c>
+      <c r="H272" s="9">
+        <v>17.832000000000001</v>
+      </c>
+      <c r="I272" s="9">
+        <v>71.328000000000003</v>
+      </c>
+      <c r="J272" s="7">
+        <f t="shared" si="8"/>
+        <v>65.978399999999993</v>
+      </c>
+      <c r="L272" s="7">
+        <f t="shared" si="9"/>
+        <v>65.978399999999993</v>
+      </c>
+      <c r="M272" s="4"/>
+    </row>
+    <row r="273" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A273" s="9">
+        <v>16</v>
+      </c>
+      <c r="B273" s="9">
+        <v>140034</v>
+      </c>
+      <c r="C273" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D273" s="9">
+        <v>2319147</v>
+      </c>
+      <c r="E273" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F273" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G273" s="9">
+        <v>29.87</v>
+      </c>
+      <c r="H273" s="9">
+        <v>5.9740000000000002</v>
+      </c>
+      <c r="I273" s="9">
+        <v>23.896000000000001</v>
+      </c>
+      <c r="J273" s="7">
+        <f t="shared" si="8"/>
+        <v>22.1038</v>
+      </c>
+      <c r="L273" s="7">
+        <f t="shared" si="9"/>
+        <v>22.1038</v>
+      </c>
+      <c r="M273" s="4"/>
+    </row>
+    <row r="274" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A274" s="9">
+        <v>17</v>
+      </c>
+      <c r="B274" s="9">
+        <v>140035</v>
+      </c>
+      <c r="C274" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D274" s="9">
+        <v>2319148</v>
+      </c>
+      <c r="E274" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F274" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G274" s="9">
+        <v>36.53</v>
+      </c>
+      <c r="H274" s="9">
+        <v>7.306</v>
+      </c>
+      <c r="I274" s="9">
+        <v>29.224</v>
+      </c>
+      <c r="J274" s="7">
+        <f t="shared" si="8"/>
+        <v>27.0322</v>
+      </c>
+      <c r="L274" s="7">
+        <f t="shared" si="9"/>
+        <v>27.0322</v>
+      </c>
+      <c r="M274" s="4"/>
+    </row>
+    <row r="275" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A275" s="9">
+        <v>18</v>
+      </c>
+      <c r="B275" s="9">
+        <v>114444</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D275" s="9">
+        <v>2319149</v>
+      </c>
+      <c r="E275" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F275" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G275" s="9">
+        <v>96.51</v>
+      </c>
+      <c r="H275" s="9">
+        <v>19.302</v>
+      </c>
+      <c r="I275" s="9">
+        <v>77.207999999999998</v>
+      </c>
+      <c r="J275" s="7">
+        <f t="shared" si="8"/>
+        <v>71.417399999999986</v>
+      </c>
+      <c r="L275" s="7">
+        <f t="shared" si="9"/>
+        <v>71.417399999999986</v>
+      </c>
+      <c r="M275" s="4"/>
+    </row>
+    <row r="276" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A276" s="9">
+        <v>19</v>
+      </c>
+      <c r="B276" s="9">
+        <v>115605</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D276" s="9">
+        <v>2319153</v>
+      </c>
+      <c r="E276" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F276" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G276" s="9">
+        <v>122.66</v>
+      </c>
+      <c r="H276" s="9">
+        <v>24.532</v>
+      </c>
+      <c r="I276" s="9">
+        <v>98.128</v>
+      </c>
+      <c r="J276" s="7">
+        <f t="shared" si="8"/>
+        <v>90.7684</v>
+      </c>
+      <c r="L276" s="7">
+        <f t="shared" si="9"/>
+        <v>90.7684</v>
+      </c>
+      <c r="M276" s="4"/>
+    </row>
+    <row r="277" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A277" s="9">
+        <v>20</v>
+      </c>
+      <c r="B277" s="9">
+        <v>116179</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D277" s="9">
+        <v>2319154</v>
+      </c>
+      <c r="E277" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F277" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G277" s="9">
+        <v>49.26</v>
+      </c>
+      <c r="H277" s="9">
+        <v>9.8520000000000003</v>
+      </c>
+      <c r="I277" s="9">
+        <v>39.408000000000001</v>
+      </c>
+      <c r="J277" s="7">
+        <f t="shared" si="8"/>
+        <v>36.452399999999997</v>
+      </c>
+      <c r="L277" s="7">
+        <f t="shared" si="9"/>
+        <v>36.452399999999997</v>
+      </c>
+      <c r="M277" s="4"/>
+    </row>
+    <row r="278" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A278" s="9">
+        <v>21</v>
+      </c>
+      <c r="B278" s="9">
+        <v>115743</v>
+      </c>
+      <c r="C278" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D278" s="9">
+        <v>182486</v>
+      </c>
+      <c r="E278" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F278" s="10">
+        <v>46219</v>
+      </c>
+      <c r="G278" s="9">
+        <v>38.36</v>
+      </c>
+      <c r="H278" s="9">
+        <v>7.6719999999999997</v>
+      </c>
+      <c r="I278" s="9">
+        <v>30.687999999999999</v>
+      </c>
+      <c r="J278" s="7">
+        <f t="shared" si="8"/>
+        <v>28.386399999999998</v>
+      </c>
+      <c r="L278" s="7">
+        <f t="shared" si="9"/>
+        <v>28.386399999999998</v>
+      </c>
+      <c r="M278" s="4"/>
+    </row>
+    <row r="279" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A279" s="9">
+        <v>22</v>
+      </c>
+      <c r="B279" s="9">
+        <v>114156</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D279" s="9">
+        <v>182370</v>
+      </c>
+      <c r="E279" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F279" s="10">
+        <v>46219</v>
+      </c>
+      <c r="G279" s="9">
+        <v>41.93</v>
+      </c>
+      <c r="H279" s="9">
+        <v>8.3859999999999992</v>
+      </c>
+      <c r="I279" s="9">
+        <v>33.543999999999997</v>
+      </c>
+      <c r="J279" s="7">
+        <f t="shared" si="8"/>
+        <v>31.028200000000002</v>
+      </c>
+      <c r="L279" s="7">
+        <f t="shared" si="9"/>
+        <v>31.028200000000002</v>
+      </c>
+      <c r="M279" s="4"/>
+    </row>
+    <row r="280" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A280" s="9">
+        <v>23</v>
+      </c>
+      <c r="B280" s="9">
+        <v>115745</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D280" s="9">
+        <v>182483</v>
+      </c>
+      <c r="E280" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F280" s="10">
+        <v>46219</v>
+      </c>
+      <c r="G280" s="9">
+        <v>25.04</v>
+      </c>
+      <c r="H280" s="9">
+        <v>5.008</v>
+      </c>
+      <c r="I280" s="9">
+        <v>20.032</v>
+      </c>
+      <c r="J280" s="7">
+        <f t="shared" si="8"/>
+        <v>18.529599999999999</v>
+      </c>
+      <c r="L280" s="7">
+        <f t="shared" si="9"/>
+        <v>18.529599999999999</v>
+      </c>
+      <c r="M280" s="4"/>
+    </row>
+    <row r="281" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A281" s="9">
+        <v>24</v>
+      </c>
+      <c r="B281" s="9">
+        <v>115744</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D281" s="9">
+        <v>182371</v>
+      </c>
+      <c r="E281" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F281" s="10">
+        <v>46219</v>
+      </c>
+      <c r="G281" s="9">
+        <v>32.25</v>
+      </c>
+      <c r="H281" s="9">
+        <v>6.45</v>
+      </c>
+      <c r="I281" s="9">
+        <v>25.8</v>
+      </c>
+      <c r="J281" s="7">
+        <f t="shared" si="8"/>
+        <v>23.864999999999998</v>
+      </c>
+      <c r="L281" s="7">
+        <f t="shared" si="9"/>
+        <v>23.864999999999998</v>
+      </c>
+      <c r="M281" s="4"/>
+    </row>
+    <row r="282" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A282" s="9">
+        <v>25</v>
+      </c>
+      <c r="B282" s="9">
+        <v>138342</v>
+      </c>
+      <c r="C282" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D282" s="9">
+        <v>184761</v>
+      </c>
+      <c r="E282" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F282" s="10">
+        <v>46230</v>
+      </c>
+      <c r="G282" s="9">
+        <v>5.56</v>
+      </c>
+      <c r="H282" s="9">
+        <v>1.1120000000000001</v>
+      </c>
+      <c r="I282" s="9">
+        <v>4.4480000000000004</v>
+      </c>
+      <c r="J282" s="7">
+        <f t="shared" si="8"/>
+        <v>4.1143999999999989</v>
+      </c>
+      <c r="L282" s="7">
+        <f t="shared" si="9"/>
+        <v>4.1143999999999989</v>
+      </c>
+      <c r="M282" s="4"/>
+    </row>
+    <row r="283" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A283" s="9">
+        <v>26</v>
+      </c>
+      <c r="B283" s="9">
+        <v>139979</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D283" s="9">
+        <v>184878</v>
+      </c>
+      <c r="E283" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F283" s="10">
+        <v>46230</v>
+      </c>
+      <c r="G283" s="9">
+        <v>22.84</v>
+      </c>
+      <c r="H283" s="9">
+        <v>4.5679999999999996</v>
+      </c>
+      <c r="I283" s="9">
+        <v>18.271999999999998</v>
+      </c>
+      <c r="J283" s="7">
+        <f t="shared" si="8"/>
+        <v>16.901600000000002</v>
+      </c>
+      <c r="L283" s="7">
+        <f t="shared" si="9"/>
+        <v>16.901600000000002</v>
+      </c>
+      <c r="M283" s="4"/>
+    </row>
+    <row r="284" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A284" s="9"/>
+      <c r="B284" s="9"/>
+      <c r="C284" s="9"/>
+      <c r="D284" s="9"/>
+      <c r="E284" s="9"/>
+      <c r="F284" s="10"/>
+      <c r="G284" s="6"/>
+      <c r="H284" s="6"/>
+      <c r="I284" s="6"/>
+      <c r="K284" s="7">
         <f>SUBTOTAL(109,Table1[المدفوع])</f>
         <v>10730.002999999997</v>
       </c>
-      <c r="M258" s="4"/>
+      <c r="M284" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ميديكسا.xlsx
+++ b/ميديكسا.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0F28C2-B06E-418C-A79E-02ADB668746D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E291B1E7-FD28-4B08-AD87-386780B31057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -382,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -391,9 +391,6 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,6 +463,12 @@
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
     <dxf>
@@ -524,12 +527,6 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -785,13 +782,13 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="رقم النموذج" dataDxfId="19" totalsRowDxfId="18"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="نوع المستفيد" dataDxfId="17" totalsRowDxfId="16"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="تاريخ البيع" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="قيمة الفاتورة" dataDxfId="11" totalsRowDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="قيمة المشاركة" dataDxfId="10" totalsRowDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="صافي القيمة" dataDxfId="9" totalsRowDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="القيمة المطلوبة" dataDxfId="8" totalsRowDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="المدفوع" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="المتبقي" dataDxfId="6" totalsRowDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{041AFAF5-9550-455C-B55D-99C85FD7E974}" name="تاريخ الدفعة" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="قيمة الفاتورة" dataDxfId="13" totalsRowDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="قيمة المشاركة" dataDxfId="12" totalsRowDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="صافي القيمة" dataDxfId="11" totalsRowDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="القيمة المطلوبة" dataDxfId="10" totalsRowDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="المدفوع" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="المتبقي" dataDxfId="8" totalsRowDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{041AFAF5-9550-455C-B55D-99C85FD7E974}" name="تاريخ الدفعة" dataDxfId="7" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11037,11 +11034,16 @@
         <f t="shared" si="6"/>
         <v>87.423599999999993</v>
       </c>
+      <c r="K236" s="7">
+        <v>87.426000000000002</v>
+      </c>
       <c r="L236" s="7">
         <f t="shared" si="7"/>
-        <v>87.423599999999993</v>
-      </c>
-      <c r="M236" s="4"/>
+        <v>-2.4000000000086175E-3</v>
+      </c>
+      <c r="M236" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="237" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
@@ -11075,11 +11077,16 @@
         <f t="shared" si="6"/>
         <v>33.181600000000003</v>
       </c>
+      <c r="K237" s="7">
+        <v>33.182000000000002</v>
+      </c>
       <c r="L237" s="7">
         <f t="shared" si="7"/>
-        <v>33.181600000000003</v>
-      </c>
-      <c r="M237" s="4"/>
+        <v>-3.9999999999906777E-4</v>
+      </c>
+      <c r="M237" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="238" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
@@ -11113,11 +11120,16 @@
         <f t="shared" si="6"/>
         <v>14.200599999999998</v>
       </c>
+      <c r="K238" s="7">
+        <v>14.201000000000001</v>
+      </c>
       <c r="L238" s="7">
         <f t="shared" si="7"/>
-        <v>14.200599999999998</v>
-      </c>
-      <c r="M238" s="4"/>
+        <v>-4.0000000000262048E-4</v>
+      </c>
+      <c r="M238" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="239" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
@@ -11151,11 +11163,16 @@
         <f t="shared" si="6"/>
         <v>135.61239999999998</v>
       </c>
+      <c r="K239" s="7">
+        <v>135.613</v>
+      </c>
       <c r="L239" s="7">
         <f t="shared" si="7"/>
-        <v>135.61239999999998</v>
-      </c>
-      <c r="M239" s="4"/>
+        <v>-6.0000000001991793E-4</v>
+      </c>
+      <c r="M239" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="240" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="2">
@@ -11189,11 +11206,16 @@
         <f t="shared" si="6"/>
         <v>44.38519999999999</v>
       </c>
+      <c r="K240" s="7">
+        <v>44.386000000000003</v>
+      </c>
       <c r="L240" s="7">
         <f t="shared" si="7"/>
-        <v>44.38519999999999</v>
-      </c>
-      <c r="M240" s="4"/>
+        <v>-8.0000000001234639E-4</v>
+      </c>
+      <c r="M240" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="241" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
@@ -11227,11 +11249,16 @@
         <f t="shared" si="6"/>
         <v>87.9786</v>
       </c>
+      <c r="K241" s="7">
+        <v>87.978999999999999</v>
+      </c>
       <c r="L241" s="7">
         <f t="shared" si="7"/>
-        <v>87.9786</v>
-      </c>
-      <c r="M241" s="4"/>
+        <v>-3.9999999999906777E-4</v>
+      </c>
+      <c r="M241" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="242" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
@@ -11265,11 +11292,16 @@
         <f t="shared" si="6"/>
         <v>142.57579999999999</v>
       </c>
+      <c r="K242" s="7">
+        <v>142.577</v>
+      </c>
       <c r="L242" s="7">
         <f t="shared" si="7"/>
-        <v>142.57579999999999</v>
-      </c>
-      <c r="M242" s="4"/>
+        <v>-1.2000000000114142E-3</v>
+      </c>
+      <c r="M242" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="243" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
@@ -11303,11 +11335,16 @@
         <f t="shared" si="6"/>
         <v>123.41720000000001</v>
       </c>
+      <c r="K243" s="7">
+        <v>123.419</v>
+      </c>
       <c r="L243" s="7">
         <f t="shared" si="7"/>
-        <v>123.41720000000001</v>
-      </c>
-      <c r="M243" s="4"/>
+        <v>-1.7999999999886995E-3</v>
+      </c>
+      <c r="M243" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="244" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
@@ -11341,11 +11378,16 @@
         <f t="shared" si="6"/>
         <v>39.094199999999994</v>
       </c>
+      <c r="K244" s="7">
+        <v>39.094999999999999</v>
+      </c>
       <c r="L244" s="7">
         <f t="shared" si="7"/>
-        <v>39.094199999999994</v>
-      </c>
-      <c r="M244" s="4"/>
+        <v>-8.0000000000524096E-4</v>
+      </c>
+      <c r="M244" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="245" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
@@ -11379,11 +11421,16 @@
         <f t="shared" si="6"/>
         <v>8.9539999999999988</v>
       </c>
+      <c r="K245" s="7">
+        <v>8.9540000000000006</v>
+      </c>
       <c r="L245" s="7">
         <f t="shared" si="7"/>
-        <v>8.9539999999999988</v>
-      </c>
-      <c r="M245" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="M245" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="246" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
@@ -11417,11 +11464,16 @@
         <f t="shared" si="6"/>
         <v>46.634799999999998</v>
       </c>
+      <c r="K246" s="7">
+        <v>47.078000000000003</v>
+      </c>
       <c r="L246" s="7">
         <f t="shared" si="7"/>
-        <v>46.634799999999998</v>
-      </c>
-      <c r="M246" s="4"/>
+        <v>-0.44320000000000448</v>
+      </c>
+      <c r="M246" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="247" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
@@ -11455,11 +11507,16 @@
         <f t="shared" si="6"/>
         <v>50.290399999999991</v>
       </c>
+      <c r="K247" s="7">
+        <v>50.289000000000001</v>
+      </c>
       <c r="L247" s="7">
         <f t="shared" si="7"/>
-        <v>50.290399999999991</v>
-      </c>
-      <c r="M247" s="4"/>
+        <v>1.3999999999896318E-3</v>
+      </c>
+      <c r="M247" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="248" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="2">
@@ -11493,11 +11550,16 @@
         <f t="shared" si="6"/>
         <v>17.9376</v>
       </c>
+      <c r="K248" s="7">
+        <v>17.937999999999999</v>
+      </c>
       <c r="L248" s="7">
         <f t="shared" si="7"/>
-        <v>17.9376</v>
-      </c>
-      <c r="M248" s="4"/>
+        <v>-3.9999999999906777E-4</v>
+      </c>
+      <c r="M248" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="249" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
@@ -11531,11 +11593,16 @@
         <f t="shared" si="6"/>
         <v>22.1038</v>
       </c>
+      <c r="K249" s="7">
+        <v>22.103999999999999</v>
+      </c>
       <c r="L249" s="7">
         <f t="shared" si="7"/>
-        <v>22.1038</v>
-      </c>
-      <c r="M249" s="4"/>
+        <v>-1.9999999999953388E-4</v>
+      </c>
+      <c r="M249" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="250" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2">
@@ -11569,11 +11636,16 @@
         <f t="shared" si="6"/>
         <v>27.0322</v>
       </c>
+      <c r="K250" s="7">
+        <v>27.032</v>
+      </c>
       <c r="L250" s="7">
         <f t="shared" si="7"/>
-        <v>27.0322</v>
-      </c>
-      <c r="M250" s="4"/>
+        <v>1.9999999999953388E-4</v>
+      </c>
+      <c r="M250" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="251" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="2">
@@ -11721,11 +11793,16 @@
         <f t="shared" si="6"/>
         <v>6.0013999999999994</v>
       </c>
+      <c r="K254" s="7">
+        <v>6.0010000000000003</v>
+      </c>
       <c r="L254" s="7">
         <f t="shared" si="7"/>
-        <v>6.0013999999999994</v>
-      </c>
-      <c r="M254" s="4"/>
+        <v>3.9999999999906777E-4</v>
+      </c>
+      <c r="M254" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="255" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="2">
@@ -11797,11 +11874,16 @@
         <f t="shared" si="6"/>
         <v>22.1556</v>
       </c>
+      <c r="K256" s="7">
+        <v>22.140999999999998</v>
+      </c>
       <c r="L256" s="7">
         <f t="shared" si="7"/>
-        <v>22.1556</v>
-      </c>
-      <c r="M256" s="4"/>
+        <v>1.4600000000001501E-2</v>
+      </c>
+      <c r="M256" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="257" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="2">
@@ -11835,45 +11917,50 @@
         <f t="shared" si="6"/>
         <v>22.910399999999999</v>
       </c>
+      <c r="K257" s="7">
+        <v>22.91</v>
+      </c>
       <c r="L257" s="7">
         <f t="shared" si="7"/>
-        <v>22.910399999999999</v>
-      </c>
-      <c r="M257" s="4"/>
+        <v>3.9999999999906777E-4</v>
+      </c>
+      <c r="M257" s="4">
+        <v>46218</v>
+      </c>
     </row>
     <row r="258" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A258" s="9">
+      <c r="A258" s="2">
         <v>1</v>
       </c>
-      <c r="B258" s="9">
+      <c r="B258" s="2">
         <v>118021</v>
       </c>
-      <c r="C258" s="9" t="s">
+      <c r="C258" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D258" s="9">
+      <c r="D258" s="2">
         <v>178721</v>
       </c>
-      <c r="E258" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F258" s="10">
+      <c r="E258" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F258" s="3">
         <v>46204</v>
       </c>
-      <c r="G258" s="9">
+      <c r="G258" s="2">
         <v>56.75</v>
       </c>
-      <c r="H258" s="9">
+      <c r="H258" s="2">
         <v>11.35</v>
       </c>
-      <c r="I258" s="9">
+      <c r="I258" s="2">
         <v>45.4</v>
       </c>
       <c r="J258" s="7">
         <f t="shared" si="6"/>
         <v>41.994999999999997</v>
       </c>
-      <c r="K258" s="8"/>
+      <c r="K258"/>
       <c r="L258" s="7">
         <f t="shared" si="7"/>
         <v>41.994999999999997</v>
@@ -11881,38 +11968,38 @@
       <c r="M258" s="4"/>
     </row>
     <row r="259" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A259" s="9">
+      <c r="A259" s="2">
         <v>2</v>
       </c>
-      <c r="B259" s="9">
+      <c r="B259" s="2">
         <v>114658</v>
       </c>
-      <c r="C259" s="9" t="s">
+      <c r="C259" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D259" s="9">
+      <c r="D259" s="2">
         <v>2316324</v>
       </c>
-      <c r="E259" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F259" s="10">
+      <c r="E259" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F259" s="3">
         <v>46204</v>
       </c>
-      <c r="G259" s="9">
+      <c r="G259" s="2">
         <v>28.75</v>
       </c>
-      <c r="H259" s="9">
+      <c r="H259" s="2">
         <v>5.75</v>
       </c>
-      <c r="I259" s="9">
+      <c r="I259" s="2">
         <v>23</v>
       </c>
       <c r="J259" s="7">
         <f t="shared" ref="J259:J283" si="8">G259*0.94-H259</f>
         <v>21.274999999999999</v>
       </c>
-      <c r="K259" s="8"/>
+      <c r="K259"/>
       <c r="L259" s="7">
         <f t="shared" ref="L259:L283" si="9">J259-K259</f>
         <v>21.274999999999999</v>
@@ -11920,38 +12007,38 @@
       <c r="M259" s="4"/>
     </row>
     <row r="260" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A260" s="9">
+      <c r="A260" s="2">
         <v>3</v>
       </c>
-      <c r="B260" s="9">
+      <c r="B260" s="2">
         <v>114156</v>
       </c>
-      <c r="C260" s="9" t="s">
+      <c r="C260" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D260" s="9">
+      <c r="D260" s="2">
         <v>2318050</v>
       </c>
-      <c r="E260" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F260" s="10">
+      <c r="E260" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F260" s="3">
         <v>46205</v>
       </c>
-      <c r="G260" s="9">
+      <c r="G260" s="2">
         <v>97.53</v>
       </c>
-      <c r="H260" s="9">
+      <c r="H260" s="2">
         <v>19.506</v>
       </c>
-      <c r="I260" s="9">
+      <c r="I260" s="2">
         <v>78.024000000000001</v>
       </c>
       <c r="J260" s="7">
         <f t="shared" si="8"/>
         <v>72.172199999999989</v>
       </c>
-      <c r="K260" s="8"/>
+      <c r="K260"/>
       <c r="L260" s="7">
         <f t="shared" si="9"/>
         <v>72.172199999999989</v>
@@ -11959,38 +12046,38 @@
       <c r="M260" s="4"/>
     </row>
     <row r="261" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A261" s="9">
+      <c r="A261" s="2">
         <v>4</v>
       </c>
-      <c r="B261" s="9">
+      <c r="B261" s="2">
         <v>139514</v>
       </c>
-      <c r="C261" s="9" t="s">
+      <c r="C261" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D261" s="9">
+      <c r="D261" s="2">
         <v>179072</v>
       </c>
-      <c r="E261" s="9" t="s">
+      <c r="E261" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F261" s="10">
+      <c r="F261" s="3">
         <v>46205</v>
       </c>
-      <c r="G261" s="9">
+      <c r="G261" s="2">
         <v>11.63</v>
       </c>
-      <c r="H261" s="9">
+      <c r="H261" s="2">
         <v>2.3260000000000001</v>
       </c>
-      <c r="I261" s="9">
+      <c r="I261" s="2">
         <v>9.3040000000000003</v>
       </c>
       <c r="J261" s="7">
         <f t="shared" si="8"/>
         <v>8.6061999999999994</v>
       </c>
-      <c r="K261" s="8"/>
+      <c r="K261"/>
       <c r="L261" s="7">
         <f t="shared" si="9"/>
         <v>8.6061999999999994</v>
@@ -11998,38 +12085,38 @@
       <c r="M261" s="4"/>
     </row>
     <row r="262" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A262" s="9">
+      <c r="A262" s="2">
         <v>5</v>
       </c>
-      <c r="B262" s="9">
+      <c r="B262" s="2">
         <v>131204</v>
       </c>
-      <c r="C262" s="9" t="s">
+      <c r="C262" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D262" s="9">
+      <c r="D262" s="2">
         <v>2319012</v>
       </c>
-      <c r="E262" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F262" s="10">
+      <c r="E262" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F262" s="3">
         <v>46207</v>
       </c>
-      <c r="G262" s="9">
+      <c r="G262" s="2">
         <v>118.14</v>
       </c>
-      <c r="H262" s="9">
+      <c r="H262" s="2">
         <v>23.628</v>
       </c>
-      <c r="I262" s="9">
+      <c r="I262" s="2">
         <v>94.512</v>
       </c>
       <c r="J262" s="7">
         <f t="shared" si="8"/>
         <v>87.423599999999993</v>
       </c>
-      <c r="K262" s="8"/>
+      <c r="K262"/>
       <c r="L262" s="7">
         <f t="shared" si="9"/>
         <v>87.423599999999993</v>
@@ -12037,38 +12124,38 @@
       <c r="M262" s="4"/>
     </row>
     <row r="263" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A263" s="9">
+      <c r="A263" s="2">
         <v>6</v>
       </c>
-      <c r="B263" s="9">
+      <c r="B263" s="2">
         <v>131232</v>
       </c>
-      <c r="C263" s="9" t="s">
+      <c r="C263" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D263" s="9">
+      <c r="D263" s="2">
         <v>2319042</v>
       </c>
-      <c r="E263" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F263" s="10">
+      <c r="E263" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F263" s="3">
         <v>46207</v>
       </c>
-      <c r="G263" s="9">
+      <c r="G263" s="2">
         <v>44.84</v>
       </c>
-      <c r="H263" s="9">
+      <c r="H263" s="2">
         <v>8.968</v>
       </c>
-      <c r="I263" s="9">
+      <c r="I263" s="2">
         <v>35.872</v>
       </c>
       <c r="J263" s="7">
         <f t="shared" si="8"/>
         <v>33.181600000000003</v>
       </c>
-      <c r="K263" s="8"/>
+      <c r="K263"/>
       <c r="L263" s="7">
         <f t="shared" si="9"/>
         <v>33.181600000000003</v>
@@ -12076,38 +12163,38 @@
       <c r="M263" s="4"/>
     </row>
     <row r="264" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A264" s="9">
+      <c r="A264" s="2">
         <v>7</v>
       </c>
-      <c r="B264" s="9">
+      <c r="B264" s="2">
         <v>132009</v>
       </c>
-      <c r="C264" s="9" t="s">
+      <c r="C264" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D264" s="9">
+      <c r="D264" s="2">
         <v>2319048</v>
       </c>
-      <c r="E264" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F264" s="10">
+      <c r="E264" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F264" s="3">
         <v>46207</v>
       </c>
-      <c r="G264" s="9">
+      <c r="G264" s="2">
         <v>25.74</v>
       </c>
-      <c r="H264" s="9">
+      <c r="H264" s="2">
         <v>5.1479999999999997</v>
       </c>
-      <c r="I264" s="9">
+      <c r="I264" s="2">
         <v>20.591999999999999</v>
       </c>
       <c r="J264" s="7">
         <f t="shared" si="8"/>
         <v>19.047599999999999</v>
       </c>
-      <c r="K264" s="8"/>
+      <c r="K264"/>
       <c r="L264" s="7">
         <f t="shared" si="9"/>
         <v>19.047599999999999</v>
@@ -12115,38 +12202,38 @@
       <c r="M264" s="4"/>
     </row>
     <row r="265" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A265" s="9">
+      <c r="A265" s="2">
         <v>8</v>
       </c>
-      <c r="B265" s="9">
+      <c r="B265" s="2">
         <v>132070</v>
       </c>
-      <c r="C265" s="9" t="s">
+      <c r="C265" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D265" s="9">
+      <c r="D265" s="2">
         <v>2319049</v>
       </c>
-      <c r="E265" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F265" s="10">
+      <c r="E265" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F265" s="3">
         <v>46207</v>
       </c>
-      <c r="G265" s="9">
+      <c r="G265" s="2">
         <v>183.26</v>
       </c>
-      <c r="H265" s="9">
+      <c r="H265" s="2">
         <v>36.652000000000001</v>
       </c>
-      <c r="I265" s="9">
+      <c r="I265" s="2">
         <v>146.608</v>
       </c>
       <c r="J265" s="7">
         <f t="shared" si="8"/>
         <v>135.61239999999998</v>
       </c>
-      <c r="K265" s="8"/>
+      <c r="K265"/>
       <c r="L265" s="7">
         <f t="shared" si="9"/>
         <v>135.61239999999998</v>
@@ -12154,38 +12241,38 @@
       <c r="M265" s="4"/>
     </row>
     <row r="266" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A266" s="9">
+      <c r="A266" s="2">
         <v>9</v>
       </c>
-      <c r="B266" s="9">
+      <c r="B266" s="2">
         <v>132129</v>
       </c>
-      <c r="C266" s="9" t="s">
+      <c r="C266" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D266" s="9">
+      <c r="D266" s="2">
         <v>2319051</v>
       </c>
-      <c r="E266" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F266" s="10">
+      <c r="E266" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F266" s="3">
         <v>46207</v>
       </c>
-      <c r="G266" s="9">
+      <c r="G266" s="2">
         <v>59.98</v>
       </c>
-      <c r="H266" s="9">
+      <c r="H266" s="2">
         <v>11.996</v>
       </c>
-      <c r="I266" s="9">
+      <c r="I266" s="2">
         <v>47.984000000000002</v>
       </c>
       <c r="J266" s="7">
         <f t="shared" si="8"/>
         <v>44.38519999999999</v>
       </c>
-      <c r="K266" s="8"/>
+      <c r="K266"/>
       <c r="L266" s="7">
         <f t="shared" si="9"/>
         <v>44.38519999999999</v>
@@ -12193,38 +12280,38 @@
       <c r="M266" s="4"/>
     </row>
     <row r="267" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A267" s="9">
+      <c r="A267" s="2">
         <v>10</v>
       </c>
-      <c r="B267" s="9">
+      <c r="B267" s="2">
         <v>134600</v>
       </c>
-      <c r="C267" s="9" t="s">
+      <c r="C267" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D267" s="9">
+      <c r="D267" s="2">
         <v>2319068</v>
       </c>
-      <c r="E267" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F267" s="10">
+      <c r="E267" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F267" s="3">
         <v>46207</v>
       </c>
-      <c r="G267" s="9">
+      <c r="G267" s="2">
         <v>118.89</v>
       </c>
-      <c r="H267" s="9">
+      <c r="H267" s="2">
         <v>23.777999999999999</v>
       </c>
-      <c r="I267" s="9">
+      <c r="I267" s="2">
         <v>95.111999999999995</v>
       </c>
       <c r="J267" s="7">
         <f t="shared" si="8"/>
         <v>87.9786</v>
       </c>
-      <c r="K267" s="8"/>
+      <c r="K267"/>
       <c r="L267" s="7">
         <f t="shared" si="9"/>
         <v>87.9786</v>
@@ -12232,38 +12319,38 @@
       <c r="M267" s="4"/>
     </row>
     <row r="268" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A268" s="9">
+      <c r="A268" s="2">
         <v>11</v>
       </c>
-      <c r="B268" s="9">
+      <c r="B268" s="2">
         <v>134714</v>
       </c>
-      <c r="C268" s="9" t="s">
+      <c r="C268" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D268" s="9">
+      <c r="D268" s="2">
         <v>2319077</v>
       </c>
-      <c r="E268" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F268" s="10">
+      <c r="E268" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F268" s="3">
         <v>46207</v>
       </c>
-      <c r="G268" s="9">
+      <c r="G268" s="2">
         <v>242.48</v>
       </c>
-      <c r="H268" s="9">
+      <c r="H268" s="2">
         <v>48.496000000000002</v>
       </c>
-      <c r="I268" s="9">
+      <c r="I268" s="2">
         <v>193.98400000000001</v>
       </c>
       <c r="J268" s="7">
         <f t="shared" si="8"/>
         <v>179.43519999999998</v>
       </c>
-      <c r="K268" s="8"/>
+      <c r="K268"/>
       <c r="L268" s="7">
         <f t="shared" si="9"/>
         <v>179.43519999999998</v>
@@ -12271,38 +12358,38 @@
       <c r="M268" s="4"/>
     </row>
     <row r="269" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A269" s="9">
+      <c r="A269" s="2">
         <v>12</v>
       </c>
-      <c r="B269" s="9">
+      <c r="B269" s="2">
         <v>137683</v>
       </c>
-      <c r="C269" s="9" t="s">
+      <c r="C269" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D269" s="9">
+      <c r="D269" s="2">
         <v>2319085</v>
       </c>
-      <c r="E269" s="9" t="s">
+      <c r="E269" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F269" s="10">
+      <c r="F269" s="3">
         <v>46207</v>
       </c>
-      <c r="G269" s="9">
+      <c r="G269" s="2">
         <v>130.43</v>
       </c>
-      <c r="H269" s="9">
+      <c r="H269" s="2">
         <v>26.085999999999999</v>
       </c>
-      <c r="I269" s="9">
+      <c r="I269" s="2">
         <v>104.34399999999999</v>
       </c>
       <c r="J269" s="7">
         <f t="shared" si="8"/>
         <v>96.518200000000007</v>
       </c>
-      <c r="K269" s="8"/>
+      <c r="K269"/>
       <c r="L269" s="7">
         <f t="shared" si="9"/>
         <v>96.518200000000007</v>
@@ -12310,31 +12397,31 @@
       <c r="M269" s="4"/>
     </row>
     <row r="270" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A270" s="9">
+      <c r="A270" s="2">
         <v>13</v>
       </c>
-      <c r="B270" s="9">
+      <c r="B270" s="2">
         <v>138275</v>
       </c>
-      <c r="C270" s="9" t="s">
+      <c r="C270" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D270" s="9">
+      <c r="D270" s="2">
         <v>2319144</v>
       </c>
-      <c r="E270" s="9" t="s">
+      <c r="E270" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F270" s="10">
+      <c r="F270" s="3">
         <v>46207</v>
       </c>
-      <c r="G270" s="9">
+      <c r="G270" s="2">
         <v>52.83</v>
       </c>
-      <c r="H270" s="9">
+      <c r="H270" s="2">
         <v>10.566000000000001</v>
       </c>
-      <c r="I270" s="9">
+      <c r="I270" s="2">
         <v>42.264000000000003</v>
       </c>
       <c r="J270" s="7">
@@ -12348,31 +12435,31 @@
       <c r="M270" s="4"/>
     </row>
     <row r="271" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A271" s="9">
+      <c r="A271" s="2">
         <v>14</v>
       </c>
-      <c r="B271" s="9">
+      <c r="B271" s="2">
         <v>139514</v>
       </c>
-      <c r="C271" s="9" t="s">
+      <c r="C271" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D271" s="9">
+      <c r="D271" s="2">
         <v>2319145</v>
       </c>
-      <c r="E271" s="9" t="s">
+      <c r="E271" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F271" s="10">
+      <c r="F271" s="3">
         <v>46207</v>
       </c>
-      <c r="G271" s="9">
+      <c r="G271" s="2">
         <v>12.1</v>
       </c>
-      <c r="H271" s="9">
+      <c r="H271" s="2">
         <v>2.42</v>
       </c>
-      <c r="I271" s="9">
+      <c r="I271" s="2">
         <v>9.68</v>
       </c>
       <c r="J271" s="7">
@@ -12386,31 +12473,31 @@
       <c r="M271" s="4"/>
     </row>
     <row r="272" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A272" s="9">
-        <v>15</v>
-      </c>
-      <c r="B272" s="9">
+      <c r="A272" s="2">
+        <v>15</v>
+      </c>
+      <c r="B272" s="2">
         <v>139979</v>
       </c>
-      <c r="C272" s="9" t="s">
+      <c r="C272" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D272" s="9">
+      <c r="D272" s="2">
         <v>2319146</v>
       </c>
-      <c r="E272" s="9" t="s">
+      <c r="E272" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F272" s="10">
+      <c r="F272" s="3">
         <v>46207</v>
       </c>
-      <c r="G272" s="9">
+      <c r="G272" s="2">
         <v>89.16</v>
       </c>
-      <c r="H272" s="9">
+      <c r="H272" s="2">
         <v>17.832000000000001</v>
       </c>
-      <c r="I272" s="9">
+      <c r="I272" s="2">
         <v>71.328000000000003</v>
       </c>
       <c r="J272" s="7">
@@ -12424,31 +12511,31 @@
       <c r="M272" s="4"/>
     </row>
     <row r="273" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A273" s="9">
+      <c r="A273" s="2">
         <v>16</v>
       </c>
-      <c r="B273" s="9">
+      <c r="B273" s="2">
         <v>140034</v>
       </c>
-      <c r="C273" s="9" t="s">
+      <c r="C273" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D273" s="9">
+      <c r="D273" s="2">
         <v>2319147</v>
       </c>
-      <c r="E273" s="9" t="s">
+      <c r="E273" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F273" s="10">
+      <c r="F273" s="3">
         <v>46207</v>
       </c>
-      <c r="G273" s="9">
+      <c r="G273" s="2">
         <v>29.87</v>
       </c>
-      <c r="H273" s="9">
+      <c r="H273" s="2">
         <v>5.9740000000000002</v>
       </c>
-      <c r="I273" s="9">
+      <c r="I273" s="2">
         <v>23.896000000000001</v>
       </c>
       <c r="J273" s="7">
@@ -12462,31 +12549,31 @@
       <c r="M273" s="4"/>
     </row>
     <row r="274" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A274" s="9">
+      <c r="A274" s="2">
         <v>17</v>
       </c>
-      <c r="B274" s="9">
+      <c r="B274" s="2">
         <v>140035</v>
       </c>
-      <c r="C274" s="9" t="s">
+      <c r="C274" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D274" s="9">
+      <c r="D274" s="2">
         <v>2319148</v>
       </c>
-      <c r="E274" s="9" t="s">
+      <c r="E274" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F274" s="10">
+      <c r="F274" s="3">
         <v>46207</v>
       </c>
-      <c r="G274" s="9">
+      <c r="G274" s="2">
         <v>36.53</v>
       </c>
-      <c r="H274" s="9">
+      <c r="H274" s="2">
         <v>7.306</v>
       </c>
-      <c r="I274" s="9">
+      <c r="I274" s="2">
         <v>29.224</v>
       </c>
       <c r="J274" s="7">
@@ -12500,31 +12587,31 @@
       <c r="M274" s="4"/>
     </row>
     <row r="275" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A275" s="9">
+      <c r="A275" s="2">
         <v>18</v>
       </c>
-      <c r="B275" s="9">
+      <c r="B275" s="2">
         <v>114444</v>
       </c>
-      <c r="C275" s="9" t="s">
+      <c r="C275" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D275" s="9">
+      <c r="D275" s="2">
         <v>2319149</v>
       </c>
-      <c r="E275" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F275" s="10">
+      <c r="E275" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F275" s="3">
         <v>46207</v>
       </c>
-      <c r="G275" s="9">
+      <c r="G275" s="2">
         <v>96.51</v>
       </c>
-      <c r="H275" s="9">
+      <c r="H275" s="2">
         <v>19.302</v>
       </c>
-      <c r="I275" s="9">
+      <c r="I275" s="2">
         <v>77.207999999999998</v>
       </c>
       <c r="J275" s="7">
@@ -12538,31 +12625,31 @@
       <c r="M275" s="4"/>
     </row>
     <row r="276" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A276" s="9">
+      <c r="A276" s="2">
         <v>19</v>
       </c>
-      <c r="B276" s="9">
+      <c r="B276" s="2">
         <v>115605</v>
       </c>
-      <c r="C276" s="9" t="s">
+      <c r="C276" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D276" s="9">
+      <c r="D276" s="2">
         <v>2319153</v>
       </c>
-      <c r="E276" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F276" s="10">
+      <c r="E276" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F276" s="3">
         <v>46207</v>
       </c>
-      <c r="G276" s="9">
+      <c r="G276" s="2">
         <v>122.66</v>
       </c>
-      <c r="H276" s="9">
+      <c r="H276" s="2">
         <v>24.532</v>
       </c>
-      <c r="I276" s="9">
+      <c r="I276" s="2">
         <v>98.128</v>
       </c>
       <c r="J276" s="7">
@@ -12576,31 +12663,31 @@
       <c r="M276" s="4"/>
     </row>
     <row r="277" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A277" s="9">
+      <c r="A277" s="2">
         <v>20</v>
       </c>
-      <c r="B277" s="9">
+      <c r="B277" s="2">
         <v>116179</v>
       </c>
-      <c r="C277" s="9" t="s">
+      <c r="C277" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D277" s="9">
+      <c r="D277" s="2">
         <v>2319154</v>
       </c>
-      <c r="E277" s="9" t="s">
+      <c r="E277" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F277" s="10">
+      <c r="F277" s="3">
         <v>46207</v>
       </c>
-      <c r="G277" s="9">
+      <c r="G277" s="2">
         <v>49.26</v>
       </c>
-      <c r="H277" s="9">
+      <c r="H277" s="2">
         <v>9.8520000000000003</v>
       </c>
-      <c r="I277" s="9">
+      <c r="I277" s="2">
         <v>39.408000000000001</v>
       </c>
       <c r="J277" s="7">
@@ -12614,31 +12701,31 @@
       <c r="M277" s="4"/>
     </row>
     <row r="278" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A278" s="9">
+      <c r="A278" s="2">
         <v>21</v>
       </c>
-      <c r="B278" s="9">
+      <c r="B278" s="2">
         <v>115743</v>
       </c>
-      <c r="C278" s="9" t="s">
+      <c r="C278" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D278" s="9">
+      <c r="D278" s="2">
         <v>182486</v>
       </c>
-      <c r="E278" s="9" t="s">
+      <c r="E278" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F278" s="10">
+      <c r="F278" s="3">
         <v>46219</v>
       </c>
-      <c r="G278" s="9">
+      <c r="G278" s="2">
         <v>38.36</v>
       </c>
-      <c r="H278" s="9">
+      <c r="H278" s="2">
         <v>7.6719999999999997</v>
       </c>
-      <c r="I278" s="9">
+      <c r="I278" s="2">
         <v>30.687999999999999</v>
       </c>
       <c r="J278" s="7">
@@ -12652,31 +12739,31 @@
       <c r="M278" s="4"/>
     </row>
     <row r="279" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A279" s="9">
+      <c r="A279" s="2">
         <v>22</v>
       </c>
-      <c r="B279" s="9">
+      <c r="B279" s="2">
         <v>114156</v>
       </c>
-      <c r="C279" s="9" t="s">
+      <c r="C279" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D279" s="9">
+      <c r="D279" s="2">
         <v>182370</v>
       </c>
-      <c r="E279" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F279" s="10">
+      <c r="E279" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F279" s="3">
         <v>46219</v>
       </c>
-      <c r="G279" s="9">
+      <c r="G279" s="2">
         <v>41.93</v>
       </c>
-      <c r="H279" s="9">
+      <c r="H279" s="2">
         <v>8.3859999999999992</v>
       </c>
-      <c r="I279" s="9">
+      <c r="I279" s="2">
         <v>33.543999999999997</v>
       </c>
       <c r="J279" s="7">
@@ -12690,31 +12777,31 @@
       <c r="M279" s="4"/>
     </row>
     <row r="280" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A280" s="9">
+      <c r="A280" s="2">
         <v>23</v>
       </c>
-      <c r="B280" s="9">
+      <c r="B280" s="2">
         <v>115745</v>
       </c>
-      <c r="C280" s="9" t="s">
+      <c r="C280" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D280" s="9">
+      <c r="D280" s="2">
         <v>182483</v>
       </c>
-      <c r="E280" s="9" t="s">
+      <c r="E280" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F280" s="10">
+      <c r="F280" s="3">
         <v>46219</v>
       </c>
-      <c r="G280" s="9">
+      <c r="G280" s="2">
         <v>25.04</v>
       </c>
-      <c r="H280" s="9">
+      <c r="H280" s="2">
         <v>5.008</v>
       </c>
-      <c r="I280" s="9">
+      <c r="I280" s="2">
         <v>20.032</v>
       </c>
       <c r="J280" s="7">
@@ -12728,31 +12815,31 @@
       <c r="M280" s="4"/>
     </row>
     <row r="281" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A281" s="9">
+      <c r="A281" s="2">
         <v>24</v>
       </c>
-      <c r="B281" s="9">
+      <c r="B281" s="2">
         <v>115744</v>
       </c>
-      <c r="C281" s="9" t="s">
+      <c r="C281" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D281" s="9">
+      <c r="D281" s="2">
         <v>182371</v>
       </c>
-      <c r="E281" s="9" t="s">
+      <c r="E281" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F281" s="10">
+      <c r="F281" s="3">
         <v>46219</v>
       </c>
-      <c r="G281" s="9">
+      <c r="G281" s="2">
         <v>32.25</v>
       </c>
-      <c r="H281" s="9">
+      <c r="H281" s="2">
         <v>6.45</v>
       </c>
-      <c r="I281" s="9">
+      <c r="I281" s="2">
         <v>25.8</v>
       </c>
       <c r="J281" s="7">
@@ -12766,31 +12853,31 @@
       <c r="M281" s="4"/>
     </row>
     <row r="282" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A282" s="9">
+      <c r="A282" s="2">
         <v>25</v>
       </c>
-      <c r="B282" s="9">
+      <c r="B282" s="2">
         <v>138342</v>
       </c>
-      <c r="C282" s="9" t="s">
+      <c r="C282" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D282" s="9">
+      <c r="D282" s="2">
         <v>184761</v>
       </c>
-      <c r="E282" s="9" t="s">
+      <c r="E282" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F282" s="10">
+      <c r="F282" s="3">
         <v>46230</v>
       </c>
-      <c r="G282" s="9">
+      <c r="G282" s="2">
         <v>5.56</v>
       </c>
-      <c r="H282" s="9">
+      <c r="H282" s="2">
         <v>1.1120000000000001</v>
       </c>
-      <c r="I282" s="9">
+      <c r="I282" s="2">
         <v>4.4480000000000004</v>
       </c>
       <c r="J282" s="7">
@@ -12804,31 +12891,31 @@
       <c r="M282" s="4"/>
     </row>
     <row r="283" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A283" s="9">
+      <c r="A283" s="2">
         <v>26</v>
       </c>
-      <c r="B283" s="9">
+      <c r="B283" s="2">
         <v>139979</v>
       </c>
-      <c r="C283" s="9" t="s">
+      <c r="C283" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D283" s="9">
+      <c r="D283" s="2">
         <v>184878</v>
       </c>
-      <c r="E283" s="9" t="s">
+      <c r="E283" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F283" s="10">
+      <c r="F283" s="3">
         <v>46230</v>
       </c>
-      <c r="G283" s="9">
+      <c r="G283" s="2">
         <v>22.84</v>
       </c>
-      <c r="H283" s="9">
+      <c r="H283" s="2">
         <v>4.5679999999999996</v>
       </c>
-      <c r="I283" s="9">
+      <c r="I283" s="2">
         <v>18.271999999999998</v>
       </c>
       <c r="J283" s="7">
@@ -12842,18 +12929,18 @@
       <c r="M283" s="4"/>
     </row>
     <row r="284" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A284" s="9"/>
-      <c r="B284" s="9"/>
-      <c r="C284" s="9"/>
-      <c r="D284" s="9"/>
-      <c r="E284" s="9"/>
-      <c r="F284" s="10"/>
+      <c r="A284" s="2"/>
+      <c r="B284" s="2"/>
+      <c r="C284" s="2"/>
+      <c r="D284" s="2"/>
+      <c r="E284" s="2"/>
+      <c r="F284" s="3"/>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
       <c r="I284" s="6"/>
       <c r="K284" s="7">
         <f>SUBTOTAL(109,Table1[المدفوع])</f>
-        <v>10730.002999999997</v>
+        <v>11662.327999999992</v>
       </c>
       <c r="M284" s="4"/>
     </row>
